--- a/sheets/대금율보/검수/추월장강.xlsx
+++ b/sheets/대금율보/검수/추월장강.xlsx
@@ -4012,15 +4012,15 @@
       <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-汰?
+汰
 –</t>
         </is>
       </c>
       <c r="M3" s="24"/>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
-林無‹
+          <t xml:space="preserve">仲
+林無
 林ㅅ</t>
         </is>
       </c>
@@ -4046,17 +4046,13 @@
       <c r="C4" s="22"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕)‹
+          <t xml:space="preserve">潕)
 –
 淋ヲ</t>
         </is>
       </c>
       <c r="E4" s="22"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="22"/>
       <c r="H4" s="21"/>
       <c r="I4" s="22"/>
@@ -4108,43 +4104,23 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲太
-仲‹
+仲
 林ㅅ</t>
         </is>
       </c>
       <c r="K5" s="22"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="22"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="22"/>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P5" s="21"/>
       <c r="Q5" s="22"/>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R5" s="21"/>
       <c r="S5" s="22"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B6" s="21"/>
       <c r="C6" s="22"/>
       <c r="D6" s="21"/>
       <c r="E6" s="22"/>
@@ -4213,17 +4189,9 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J7" s="21"/>
       <c r="K7" s="22"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L7" s="21"/>
       <c r="M7" s="22"/>
       <c r="N7" s="21"/>
       <c r="O7" s="22"/>
@@ -4250,8 +4218,7 @@
         <is>
           <t xml:space="preserve">–
 㳞汰
-㳞
-‹</t>
+㳞</t>
         </is>
       </c>
       <c r="E8" s="22"/>
@@ -4263,11 +4230,7 @@
         </is>
       </c>
       <c r="G8" s="22"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="22"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
@@ -4287,22 +4250,14 @@
       <c r="M8" s="22"/>
       <c r="N8" s="21"/>
       <c r="O8" s="22"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="22"/>
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B9" s="21"/>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
@@ -4312,7 +4267,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G9" s="24"/>
@@ -4342,7 +4297,7 @@
         <is>
           <t xml:space="preserve">潢無
 潢汰
-汰‹</t>
+汰</t>
         </is>
       </c>
       <c r="O9" s="22"/>
@@ -4354,11 +4309,7 @@
         </is>
       </c>
       <c r="Q9" s="22"/>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
@@ -4375,11 +4326,7 @@
       <c r="E10" s="22"/>
       <c r="F10" s="21"/>
       <c r="G10" s="22"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="22"/>
       <c r="J10" s="21"/>
       <c r="K10" s="22"/>
@@ -4410,17 +4357,9 @@
         </is>
       </c>
       <c r="C11" s="22"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="22"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F11" s="21"/>
       <c r="G11" s="22"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
@@ -4434,27 +4373,15 @@
         <is>
           <t xml:space="preserve">潢無
 潢汰
-汰‹</t>
+汰</t>
         </is>
       </c>
       <c r="K11" s="22"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L11" s="21"/>
       <c r="M11" s="22"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N11" s="21"/>
       <c r="O11" s="22"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P11" s="21"/>
       <c r="Q11" s="22"/>
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
@@ -4538,11 +4465,7 @@
       <c r="G13" s="22"/>
       <c r="H13" s="21"/>
       <c r="I13" s="22"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="22"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4573,7 +4496,7 @@
       <c r="C14" s="22"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢?</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -4585,11 +4508,7 @@
         </is>
       </c>
       <c r="G14" s="22"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="22"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
@@ -4599,11 +4518,7 @@
         </is>
       </c>
       <c r="K14" s="22"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="22"/>
       <c r="N14" s="21"/>
       <c r="O14" s="22"/>
@@ -4611,7 +4526,7 @@
       <c r="Q14" s="22"/>
       <c r="R14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="S14" s="24"/>
@@ -4645,16 +4560,12 @@
       <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕)
-–‹
+–
 淋ヲ</t>
         </is>
       </c>
       <c r="O15" s="22"/>
-      <c r="P15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P15" s="21"/>
       <c r="Q15" s="22"/>
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
@@ -4663,17 +4574,9 @@
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D16" s="21"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F16" s="21"/>
       <c r="G16" s="22"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
@@ -4681,17 +4584,9 @@
         </is>
       </c>
       <c r="I16" s="22"/>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J16" s="21"/>
       <c r="K16" s="22"/>
-      <c r="L16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L16" s="21"/>
       <c r="M16" s="22"/>
       <c r="N16" s="21"/>
       <c r="O16" s="22"/>
@@ -4703,11 +4598,7 @@
         </is>
       </c>
       <c r="Q16" s="22"/>
-      <c r="R16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R16" s="21"/>
       <c r="S16" s="22"/>
     </row>
     <row r="17" ht="56" customHeight="1">

--- a/sheets/대금율보/검수/추월장강.xlsx
+++ b/sheets/대금율보/검수/추월장강.xlsx
@@ -3939,30 +3939,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="90.91" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="101.66" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="S3" s="26"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="101.66" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="101.66" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -4118,7 +4118,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="101.66" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="101.66" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="101.66" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="101.66" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4312,7 +4312,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="101.66" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="101.66" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="101.66" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4443,7 +4443,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="101.66" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="101.66" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="101.66" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4570,7 +4570,7 @@
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="101.66" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -4601,7 +4601,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="101.66" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="101.66" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -4701,6 +4701,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
 </worksheet>
 </file>